--- a/writing/figures/plantago-tables.xlsx
+++ b/writing/figures/plantago-tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailarizona-my.sharepoint.com/personal/maddiewallace_arizona_edu/Documents/01-research/plantago-TGP-ch1/writing/figures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madeleinewallace/Desktop/01-research/plantago-TGP/writing/figures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2805" documentId="8_{783D7B2A-45CC-2940-9A74-8D1866CE59F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42838FF2-2732-9945-A6D9-21ED2B00F806}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EFF2F9-BD43-E748-A65C-D1BEFFAF45AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="500" windowWidth="26500" windowHeight="16220" activeTab="1" xr2:uid="{473D842E-314B-8144-B51C-7F7FF6CAD569}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19660" activeTab="4" xr2:uid="{473D842E-314B-8144-B51C-7F7FF6CAD569}"/>
   </bookViews>
   <sheets>
     <sheet name="table 2" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="231">
   <si>
     <t>trait</t>
   </si>
@@ -170,12 +170,6 @@
     <t>SE</t>
   </si>
   <si>
-    <t>control</t>
-  </si>
-  <si>
-    <t>drought</t>
-  </si>
-  <si>
     <t>CC</t>
   </si>
   <si>
@@ -204,9 +198,6 @@
   </si>
   <si>
     <t>mortality status</t>
-  </si>
-  <si>
-    <t>IS CD WORSE?</t>
   </si>
   <si>
     <t>F = 2.6995</t>
@@ -398,9 +389,6 @@
     <t>NM</t>
   </si>
   <si>
-    <t>** add in all traits!</t>
-  </si>
-  <si>
     <t>F = 42.1948***</t>
   </si>
   <si>
@@ -805,6 +793,30 @@
   </si>
   <si>
     <t>-0.292***</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>HH</t>
+  </si>
+  <si>
+    <t>IS HL WORSE?</t>
+  </si>
+  <si>
+    <t>HL</t>
+  </si>
+  <si>
+    <t>LH</t>
+  </si>
+  <si>
+    <t>LL</t>
+  </si>
+  <si>
+    <t>** aLL in all traits!</t>
   </si>
 </sst>
 </file>
@@ -902,19 +914,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -925,6 +924,19 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1525,56 +1537,56 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
@@ -1975,7 +1987,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="49" customHeight="1">
       <c r="A1" s="78" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B1" s="78"/>
       <c r="C1" s="78"/>
@@ -2008,7 +2020,7 @@
     </row>
     <row r="3" spans="1:9" ht="18" customHeight="1">
       <c r="A3" s="46" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
@@ -2021,13 +2033,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E4" s="6">
         <v>0.13</v>
@@ -2041,13 +2053,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E5" s="6">
         <v>0.317</v>
@@ -2061,13 +2073,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6">
         <v>0.22500000000000001</v>
@@ -2081,13 +2093,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E7" s="6">
         <v>2E-3</v>
@@ -2106,7 +2118,7 @@
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1">
       <c r="A9" s="46" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B9" s="43"/>
       <c r="C9" s="43"/>
@@ -2119,13 +2131,13 @@
         <v>21</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E10" s="6">
         <v>7.6999999999999999E-2</v>
@@ -2139,13 +2151,13 @@
         <v>5</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E11" s="6">
         <v>1.7000000000000001E-2</v>
@@ -2159,13 +2171,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E12" s="6">
         <v>8.0000000000000002E-3</v>
@@ -2179,13 +2191,13 @@
         <v>7</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E13" s="6">
         <v>0.03</v>
@@ -2204,7 +2216,7 @@
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1">
       <c r="A15" s="46" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="43"/>
@@ -2214,16 +2226,16 @@
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1">
       <c r="A16" s="41" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E16" s="6">
         <v>1.7000000000000001E-2</v>
@@ -2242,7 +2254,7 @@
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1">
       <c r="A18" s="46" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B18" s="46"/>
       <c r="C18" s="41"/>
@@ -2252,16 +2264,16 @@
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1">
       <c r="A19" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>69</v>
-      </c>
       <c r="D19" s="43" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E19" s="6">
         <v>4.7E-2</v>
@@ -2272,7 +2284,7 @@
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1">
       <c r="A20" s="41" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B20" s="41"/>
       <c r="C20" s="41"/>
@@ -2282,16 +2294,16 @@
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1">
       <c r="A21" s="55" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C21" s="46" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E21" s="6">
         <v>0.14699999999999999</v>
@@ -2302,13 +2314,13 @@
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1">
       <c r="A22" s="55" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D22" s="41"/>
       <c r="E22" s="6"/>
@@ -2316,7 +2328,7 @@
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1">
       <c r="A23" s="41" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
@@ -2326,16 +2338,16 @@
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1">
       <c r="A24" s="55" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D24" s="41" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E24" s="6">
         <v>0.48199999999999998</v>
@@ -2346,13 +2358,13 @@
     </row>
     <row r="25" spans="1:6" ht="18" customHeight="1">
       <c r="A25" s="55" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C25" s="46" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D25" s="41"/>
       <c r="E25" s="6"/>
@@ -2363,13 +2375,13 @@
         <v>11</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E26" s="41">
         <v>0.22600000000000001</v>
@@ -2383,13 +2395,13 @@
         <v>8</v>
       </c>
       <c r="B27" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D27" s="57" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E27" s="6">
         <v>0.27700000000000002</v>
@@ -2437,7 +2449,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="49" customHeight="1">
       <c r="A1" s="78" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B1" s="78"/>
       <c r="C1" s="78"/>
@@ -2463,19 +2475,19 @@
         <v>17</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E2" s="41" t="s">
         <v>18</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G2" s="41" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H2" s="41" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I2" s="41" t="s">
         <v>19</v>
@@ -2486,7 +2498,7 @@
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1">
       <c r="A3" s="46" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
@@ -2503,25 +2515,25 @@
         <v>1</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C4" s="48" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D4" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="58" t="s">
         <v>105</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="G4" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="H4" s="58" t="s">
-        <v>109</v>
       </c>
       <c r="I4" s="6">
         <v>0.14099999999999999</v>
@@ -2535,25 +2547,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E5" s="43" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G5" s="48" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H5" s="43" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I5" s="6">
         <v>0.34499999999999997</v>
@@ -2567,25 +2579,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E6" s="43" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I6" s="6">
         <v>0.23435890000000001</v>
@@ -2599,25 +2611,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E7" s="43" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F7" s="43" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H7" s="43" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I7" s="6">
         <v>8.742306E-3</v>
@@ -2640,7 +2652,7 @@
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1">
       <c r="A9" s="46" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B9" s="43"/>
       <c r="C9" s="43"/>
@@ -2657,25 +2669,25 @@
         <v>21</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I10" s="6">
         <v>0.1011802</v>
@@ -2689,25 +2701,25 @@
         <v>5</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H11" s="58" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I11" s="6">
         <v>2.517138E-2</v>
@@ -2721,25 +2733,25 @@
         <v>6</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F12" s="43" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I12" s="6">
         <v>1.601876E-2</v>
@@ -2753,25 +2765,25 @@
         <v>7</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E13" s="43" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H13" s="43" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I13" s="6">
         <v>3.0825140000000001E-2</v>
@@ -2794,7 +2806,7 @@
     </row>
     <row r="15" spans="1:13" ht="18" customHeight="1">
       <c r="A15" s="46" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="43"/>
@@ -2808,28 +2820,28 @@
     </row>
     <row r="16" spans="1:13" ht="18" customHeight="1">
       <c r="A16" s="41" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E16" s="43" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F16" s="43" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G16" s="48" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H16" s="43" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I16" s="6">
         <v>2.624553E-2</v>
@@ -2852,7 +2864,7 @@
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1">
       <c r="A18" s="46" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B18" s="43"/>
       <c r="C18" s="43"/>
@@ -2866,28 +2878,28 @@
     </row>
     <row r="19" spans="1:10" ht="18" customHeight="1">
       <c r="A19" s="41" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F19" s="43" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H19" s="43" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I19" s="6">
         <v>5.7732789999999999E-2</v>
@@ -2898,7 +2910,7 @@
     </row>
     <row r="20" spans="1:10" ht="18" customHeight="1">
       <c r="A20" s="41" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B20" s="41"/>
       <c r="C20" s="41"/>
@@ -2912,28 +2924,28 @@
     </row>
     <row r="21" spans="1:10" ht="18" customHeight="1">
       <c r="A21" s="55" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C21" s="46" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G21" s="46" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H21" s="60" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I21" s="6">
         <v>0.26300000000000001</v>
@@ -2944,16 +2956,16 @@
     </row>
     <row r="22" spans="1:10" ht="18" customHeight="1">
       <c r="A22" s="55" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E22" s="41"/>
       <c r="F22" s="41"/>
@@ -2964,7 +2976,7 @@
     </row>
     <row r="23" spans="1:10" ht="18" customHeight="1">
       <c r="A23" s="41" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
@@ -2978,48 +2990,48 @@
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1">
       <c r="A24" s="55" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B24" s="41" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F24" s="41" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G24" s="47" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H24" s="41" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="I24" s="6">
         <v>0.30499999999999999</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1">
       <c r="A25" s="55" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C25" s="46" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D25" s="46" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E25" s="41"/>
       <c r="F25" s="41"/>
@@ -3033,25 +3045,25 @@
         <v>11</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D26" s="45" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E26" s="56" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F26" s="45" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G26" s="45" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H26" s="45" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I26" s="6">
         <v>0.2698161</v>
@@ -3065,25 +3077,25 @@
         <v>8</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E27" s="57" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G27" s="41" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H27" s="41" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I27" s="6">
         <v>0.28999009999999997</v>
@@ -3122,7 +3134,7 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="53" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -3144,61 +3156,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="29" thickBot="1">
-      <c r="A1" s="65"/>
-      <c r="B1" s="66" t="s">
+      <c r="A1" s="61"/>
+      <c r="B1" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="65" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" thickBot="1">
+      <c r="A2" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="67">
+        <v>-6.0400000000000002E-2</v>
+      </c>
+      <c r="C2" s="68">
+        <v>-9.2999999999999999E-2</v>
+      </c>
+      <c r="D2" s="69" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2" s="70">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F2" s="71">
+        <v>-3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28" customHeight="1" thickBot="1">
+      <c r="A3" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="67">
+        <v>0.105</v>
+      </c>
+      <c r="C3" s="68">
+        <v>0.121</v>
+      </c>
+      <c r="D3" s="68">
+        <v>-5.0999999999999997E-2</v>
+      </c>
+      <c r="E3" s="72" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" s="73" t="s">
         <v>222</v>
-      </c>
-      <c r="C1" s="67" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="68" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1">
-      <c r="A2" s="70" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="71">
-        <v>-6.0400000000000002E-2</v>
-      </c>
-      <c r="C2" s="72">
-        <v>-9.2999999999999999E-2</v>
-      </c>
-      <c r="D2" s="73" t="s">
-        <v>224</v>
-      </c>
-      <c r="E2" s="74">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="F2" s="75">
-        <v>-3.4000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A3" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="71">
-        <v>0.105</v>
-      </c>
-      <c r="C3" s="72">
-        <v>0.121</v>
-      </c>
-      <c r="D3" s="72">
-        <v>-5.0999999999999997E-2</v>
-      </c>
-      <c r="E3" s="76" t="s">
-        <v>225</v>
-      </c>
-      <c r="F3" s="77" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3314,7 +3326,7 @@
         <v>24</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>26</v>
@@ -3325,7 +3337,7 @@
       <c r="G1" s="22"/>
       <c r="H1" s="22"/>
       <c r="I1" s="22" t="s">
-        <v>40</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14" customHeight="1">
@@ -3333,13 +3345,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E2" s="14">
         <v>0.38200000000000001</v>
@@ -3351,13 +3363,13 @@
     <row r="3" spans="1:9" ht="16" customHeight="1">
       <c r="A3" s="86"/>
       <c r="B3" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E3" s="15">
         <v>0.246</v>
@@ -3369,13 +3381,13 @@
     <row r="4" spans="1:9" ht="16" customHeight="1">
       <c r="A4" s="86"/>
       <c r="B4" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E4" s="15">
         <v>0.40699999999999997</v>
@@ -3387,13 +3399,13 @@
     <row r="5" spans="1:9" ht="17" customHeight="1" thickBot="1">
       <c r="A5" s="87"/>
       <c r="B5" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E5" s="16">
         <v>0.245</v>
@@ -3407,13 +3419,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E6" s="19">
         <v>0.157</v>
@@ -3425,13 +3437,13 @@
     <row r="7" spans="1:9" ht="16" customHeight="1">
       <c r="A7" s="86"/>
       <c r="B7" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E7" s="15">
         <v>6.0100000000000001E-2</v>
@@ -3443,13 +3455,13 @@
     <row r="8" spans="1:9" ht="16" customHeight="1">
       <c r="A8" s="86"/>
       <c r="B8" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E8" s="15">
         <v>0.16400000000000001</v>
@@ -3461,13 +3473,13 @@
     <row r="9" spans="1:9" ht="17" customHeight="1" thickBot="1">
       <c r="A9" s="87"/>
       <c r="B9" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E9" s="16">
         <v>5.7099999999999998E-2</v>
@@ -3481,13 +3493,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E10" s="19">
         <v>0.53900000000000003</v>
@@ -3499,13 +3511,13 @@
     <row r="11" spans="1:9" ht="16" customHeight="1">
       <c r="A11" s="86"/>
       <c r="B11" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E11" s="15">
         <v>0.30599999999999999</v>
@@ -3517,13 +3529,13 @@
     <row r="12" spans="1:9" ht="16" customHeight="1">
       <c r="A12" s="86"/>
       <c r="B12" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E12" s="15">
         <v>0.57099999999999995</v>
@@ -3535,13 +3547,13 @@
     <row r="13" spans="1:9" ht="17" customHeight="1" thickBot="1">
       <c r="A13" s="87"/>
       <c r="B13" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E13" s="16">
         <v>0.30199999999999999</v>
@@ -3555,13 +3567,13 @@
         <v>21</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E14" s="19">
         <v>3.51</v>
@@ -3573,13 +3585,13 @@
     <row r="15" spans="1:9" ht="16" customHeight="1">
       <c r="A15" s="86"/>
       <c r="B15" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E15" s="15">
         <v>5.17</v>
@@ -3591,13 +3603,13 @@
     <row r="16" spans="1:9" ht="16" customHeight="1">
       <c r="A16" s="86"/>
       <c r="B16" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E16" s="15">
         <v>3.8</v>
@@ -3609,13 +3621,13 @@
     <row r="17" spans="1:6" ht="17" customHeight="1" thickBot="1">
       <c r="A17" s="87"/>
       <c r="B17" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E17" s="16">
         <v>4.9800000000000004</v>
@@ -3629,13 +3641,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E18" s="19">
         <v>4.91</v>
@@ -3647,13 +3659,13 @@
     <row r="19" spans="1:6" ht="16" customHeight="1">
       <c r="A19" s="86"/>
       <c r="B19" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E19" s="15">
         <v>4.72</v>
@@ -3665,13 +3677,13 @@
     <row r="20" spans="1:6" ht="16" customHeight="1">
       <c r="A20" s="86"/>
       <c r="B20" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E20" s="15">
         <v>5.17</v>
@@ -3683,13 +3695,13 @@
     <row r="21" spans="1:6" ht="17" customHeight="1" thickBot="1">
       <c r="A21" s="87"/>
       <c r="B21" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E21" s="16">
         <v>5.16</v>
@@ -3703,13 +3715,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E22" s="19">
         <v>1.2</v>
@@ -3721,13 +3733,13 @@
     <row r="23" spans="1:6" ht="16" customHeight="1">
       <c r="A23" s="86"/>
       <c r="B23" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E23" s="15">
         <v>1.04</v>
@@ -3739,13 +3751,13 @@
     <row r="24" spans="1:6" ht="16" customHeight="1">
       <c r="A24" s="86"/>
       <c r="B24" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E24" s="15">
         <v>1.24</v>
@@ -3757,13 +3769,13 @@
     <row r="25" spans="1:6" ht="17" customHeight="1" thickBot="1">
       <c r="A25" s="87"/>
       <c r="B25" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E25" s="16">
         <v>1.08</v>
@@ -3777,13 +3789,13 @@
         <v>6</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E26" s="39">
         <v>109.11</v>
@@ -3795,13 +3807,13 @@
     <row r="27" spans="1:6" ht="16" customHeight="1">
       <c r="A27" s="86"/>
       <c r="B27" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E27" s="17">
         <v>115.4</v>
@@ -3813,13 +3825,13 @@
     <row r="28" spans="1:6" ht="16" customHeight="1">
       <c r="A28" s="86"/>
       <c r="B28" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E28" s="17">
         <v>106.37</v>
@@ -3831,16 +3843,16 @@
     <row r="29" spans="1:6" ht="17" customHeight="1" thickBot="1">
       <c r="A29" s="87"/>
       <c r="B29" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F29" s="16">
         <v>3.04</v>
@@ -3851,13 +3863,13 @@
         <v>7</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E30" s="19">
         <v>0.372</v>
@@ -3869,13 +3881,13 @@
     <row r="31" spans="1:6" ht="16" customHeight="1">
       <c r="A31" s="86"/>
       <c r="B31" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E31" s="15">
         <v>0.44500000000000001</v>
@@ -3887,13 +3899,13 @@
     <row r="32" spans="1:6" ht="16" customHeight="1">
       <c r="A32" s="86"/>
       <c r="B32" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E32" s="15">
         <v>0.35899999999999999</v>
@@ -3905,13 +3917,13 @@
     <row r="33" spans="1:7" ht="17" customHeight="1" thickBot="1">
       <c r="A33" s="87"/>
       <c r="B33" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E33" s="16">
         <v>0.4</v>
@@ -3922,16 +3934,16 @@
     </row>
     <row r="34" spans="1:7" ht="14" customHeight="1">
       <c r="A34" s="85" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E34" s="19">
         <f>1-0.839</f>
@@ -3944,13 +3956,13 @@
     <row r="35" spans="1:7" ht="16" customHeight="1">
       <c r="A35" s="86"/>
       <c r="B35" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E35" s="15">
         <f>1-0.88</f>
@@ -3963,13 +3975,13 @@
     <row r="36" spans="1:7" ht="16" customHeight="1">
       <c r="A36" s="86"/>
       <c r="B36" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E36" s="15">
         <f>1-0.801</f>
@@ -3982,13 +3994,13 @@
     <row r="37" spans="1:7" ht="17" customHeight="1" thickBot="1">
       <c r="A37" s="88"/>
       <c r="B37" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E37" s="16">
         <f>1-0.871</f>
@@ -4000,16 +4012,16 @@
     </row>
     <row r="38" spans="1:7" ht="17" customHeight="1">
       <c r="A38" s="82" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E38" s="19">
         <v>0.215</v>
@@ -4022,13 +4034,13 @@
     <row r="39" spans="1:7" ht="17" customHeight="1">
       <c r="A39" s="83"/>
       <c r="B39" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E39" s="15">
         <v>0.10299999999999999</v>
@@ -4041,13 +4053,13 @@
     <row r="40" spans="1:7" ht="17" customHeight="1">
       <c r="A40" s="83"/>
       <c r="B40" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E40" s="15">
         <v>0.29299999999999998</v>
@@ -4059,13 +4071,13 @@
     <row r="41" spans="1:7" ht="17" customHeight="1" thickBot="1">
       <c r="A41" s="84"/>
       <c r="B41" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E41" s="16">
         <v>0.17399999999999999</v>
@@ -4079,13 +4091,13 @@
         <v>8</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E42" s="19">
         <v>3.6900000000000002E-2</v>
@@ -4097,13 +4109,13 @@
     <row r="43" spans="1:7" ht="16" customHeight="1">
       <c r="A43" s="90"/>
       <c r="B43" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E43" s="15">
         <v>2.0799999999999999E-2</v>
@@ -4115,13 +4127,13 @@
     <row r="44" spans="1:7" ht="16" customHeight="1">
       <c r="A44" s="90"/>
       <c r="B44" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E44" s="15">
         <v>4.5900000000000003E-2</v>
@@ -4133,13 +4145,13 @@
     <row r="45" spans="1:7" ht="17" customHeight="1" thickBot="1">
       <c r="A45" s="91"/>
       <c r="B45" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E45" s="16">
         <v>1.0800000000000001E-2</v>
@@ -4153,13 +4165,13 @@
         <v>11</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E46" s="21">
         <v>46.752000000000002</v>
@@ -4171,13 +4183,13 @@
     <row r="47" spans="1:7" ht="16" customHeight="1">
       <c r="A47" s="80"/>
       <c r="B47" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E47" s="18">
         <v>28.289000000000001</v>
@@ -4189,13 +4201,13 @@
     <row r="48" spans="1:7" ht="16" customHeight="1">
       <c r="A48" s="80"/>
       <c r="B48" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E48" s="18">
         <v>55.892000000000003</v>
@@ -4207,13 +4219,13 @@
     <row r="49" spans="1:6" ht="17" customHeight="1" thickBot="1">
       <c r="A49" s="81"/>
       <c r="B49" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E49" s="20">
         <v>15.827</v>
@@ -4227,13 +4239,13 @@
         <v>12</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E50" s="19">
         <v>2.38</v>
@@ -4245,13 +4257,13 @@
     <row r="51" spans="1:6" ht="16" customHeight="1">
       <c r="A51" s="80"/>
       <c r="B51" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E51" s="15">
         <v>1.7</v>
@@ -4263,13 +4275,13 @@
     <row r="52" spans="1:6" ht="16" customHeight="1">
       <c r="A52" s="80"/>
       <c r="B52" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E52" s="15">
         <v>2.59</v>
@@ -4281,13 +4293,13 @@
     <row r="53" spans="1:6" ht="17" customHeight="1" thickBot="1">
       <c r="A53" s="81"/>
       <c r="B53" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E53" s="16">
         <v>1.63</v>
@@ -4301,13 +4313,13 @@
         <v>13</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E54" s="21">
         <v>41.112000000000002</v>
@@ -4319,13 +4331,13 @@
     <row r="55" spans="1:6" ht="16" customHeight="1">
       <c r="A55" s="80"/>
       <c r="B55" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="E55" s="15">
         <v>42.628999999999998</v>
@@ -4337,13 +4349,13 @@
     <row r="56" spans="1:6" ht="16" customHeight="1">
       <c r="A56" s="80"/>
       <c r="B56" s="7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="E56" s="18">
         <v>40.210999999999999</v>
@@ -4355,13 +4367,13 @@
     <row r="57" spans="1:6" ht="17" customHeight="1" thickBot="1">
       <c r="A57" s="81"/>
       <c r="B57" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="E57" s="20">
         <v>45.094999999999999</v>
@@ -4413,10 +4425,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="52" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D1" s="29" t="s">
         <v>26</v>
@@ -4433,7 +4445,7 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D2" s="8">
         <v>0.27400000000000002</v>
@@ -4442,7 +4454,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>98</v>
+        <v>230</v>
       </c>
       <c r="H2" s="32"/>
       <c r="M2" s="31"/>
@@ -4460,7 +4472,7 @@
       <c r="A3" s="95"/>
       <c r="B3" s="93"/>
       <c r="C3" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D3" s="8">
         <v>9.9000000000000005E-2</v>
@@ -4485,7 +4497,7 @@
       <c r="A4" s="95"/>
       <c r="B4" s="93"/>
       <c r="C4" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D4" s="8">
         <v>0.21199999999999999</v>
@@ -4510,7 +4522,7 @@
       <c r="A5" s="95"/>
       <c r="B5" s="94"/>
       <c r="C5" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D5" s="27">
         <v>9.5000000000000001E-2</v>
@@ -4537,7 +4549,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D6" s="24">
         <v>0.14399999999999999</v>
@@ -4562,7 +4574,7 @@
       <c r="A7" s="95"/>
       <c r="B7" s="93"/>
       <c r="C7" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D7" s="8">
         <v>8.5000000000000006E-2</v>
@@ -4587,7 +4599,7 @@
       <c r="A8" s="95"/>
       <c r="B8" s="93"/>
       <c r="C8" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D8" s="8">
         <v>0.112</v>
@@ -4612,13 +4624,13 @@
       <c r="A9" s="95"/>
       <c r="B9" s="94"/>
       <c r="C9" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D9" s="27">
         <v>1.9E-2</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
@@ -4639,7 +4651,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D10" s="24">
         <v>0.182</v>
@@ -4664,7 +4676,7 @@
       <c r="A11" s="95"/>
       <c r="B11" s="93"/>
       <c r="C11" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D11" s="8">
         <v>5.0999999999999997E-2</v>
@@ -4689,7 +4701,7 @@
       <c r="A12" s="95"/>
       <c r="B12" s="93"/>
       <c r="C12" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D12" s="8">
         <v>0.17699999999999999</v>
@@ -4714,7 +4726,7 @@
       <c r="A13" s="95"/>
       <c r="B13" s="94"/>
       <c r="C13" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D13" s="27">
         <v>5.8999999999999997E-2</v>
@@ -4741,7 +4753,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D14" s="24">
         <v>0.156</v>
@@ -4766,7 +4778,7 @@
       <c r="A15" s="95"/>
       <c r="B15" s="93"/>
       <c r="C15" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D15" s="8">
         <v>6.7000000000000004E-2</v>
@@ -4791,7 +4803,7 @@
       <c r="A16" s="95"/>
       <c r="B16" s="93"/>
       <c r="C16" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D16" s="8">
         <v>0.17199999999999999</v>
@@ -4816,7 +4828,7 @@
       <c r="A17" s="95"/>
       <c r="B17" s="94"/>
       <c r="C17" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D17" s="27">
         <v>4.2999999999999997E-2</v>
@@ -4843,7 +4855,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D18" s="34">
         <v>0.16</v>
@@ -4868,7 +4880,7 @@
       <c r="A19" s="95"/>
       <c r="B19" s="93"/>
       <c r="C19" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D19" s="33">
         <v>0.06</v>
@@ -4893,7 +4905,7 @@
       <c r="A20" s="95"/>
       <c r="B20" s="93"/>
       <c r="C20" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D20" s="8">
         <v>0.23599999999999999</v>
@@ -4918,7 +4930,7 @@
       <c r="A21" s="95"/>
       <c r="B21" s="94"/>
       <c r="C21" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D21" s="27">
         <v>7.8E-2</v>
@@ -4945,7 +4957,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D22" s="24">
         <v>0.16800000000000001</v>
@@ -4970,7 +4982,7 @@
       <c r="A23" s="95"/>
       <c r="B23" s="93"/>
       <c r="C23" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D23" s="8">
         <v>4.2000000000000003E-2</v>
@@ -4995,7 +5007,7 @@
       <c r="A24" s="95"/>
       <c r="B24" s="93"/>
       <c r="C24" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D24" s="8">
         <v>0.153</v>
@@ -5020,7 +5032,7 @@
       <c r="A25" s="95"/>
       <c r="B25" s="94"/>
       <c r="C25" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D25" s="27">
         <v>4.4999999999999998E-2</v>
@@ -5047,7 +5059,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D26" s="24">
         <v>0.17399999999999999</v>
@@ -5072,7 +5084,7 @@
       <c r="A27" s="95"/>
       <c r="B27" s="93"/>
       <c r="C27" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D27" s="8">
         <v>8.7999999999999995E-2</v>
@@ -5097,7 +5109,7 @@
       <c r="A28" s="95"/>
       <c r="B28" s="93"/>
       <c r="C28" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D28" s="8">
         <v>0.18099999999999999</v>
@@ -5122,7 +5134,7 @@
       <c r="A29" s="95"/>
       <c r="B29" s="94"/>
       <c r="C29" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D29" s="27">
         <v>6.5000000000000002E-2</v>
@@ -5149,7 +5161,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D30" s="24">
         <v>9.5000000000000001E-2</v>
@@ -5174,7 +5186,7 @@
       <c r="A31" s="95"/>
       <c r="B31" s="93"/>
       <c r="C31" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D31" s="8">
         <v>5.8999999999999997E-2</v>
@@ -5199,7 +5211,7 @@
       <c r="A32" s="95"/>
       <c r="B32" s="93"/>
       <c r="C32" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D32" s="8">
         <v>8.7999999999999995E-2</v>
@@ -5224,7 +5236,7 @@
       <c r="A33" s="95"/>
       <c r="B33" s="94"/>
       <c r="C33" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D33" s="27">
         <v>4.9000000000000002E-2</v>
@@ -5251,7 +5263,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D34" s="24">
         <v>0.105</v>
@@ -5276,7 +5288,7 @@
       <c r="A35" s="95"/>
       <c r="B35" s="93"/>
       <c r="C35" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D35" s="8">
         <v>3.9E-2</v>
@@ -5301,7 +5313,7 @@
       <c r="A36" s="95"/>
       <c r="B36" s="93"/>
       <c r="C36" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D36" s="33">
         <v>0.46</v>
@@ -5326,7 +5338,7 @@
       <c r="A37" s="95"/>
       <c r="B37" s="94"/>
       <c r="C37" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D37" s="27">
         <v>2.4E-2</v>
@@ -5353,7 +5365,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D38" s="24">
         <v>0.19900000000000001</v>
@@ -5378,7 +5390,7 @@
       <c r="A39" s="95"/>
       <c r="B39" s="93"/>
       <c r="C39" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D39" s="8">
         <v>5.3999999999999999E-2</v>
@@ -5403,7 +5415,7 @@
       <c r="A40" s="95"/>
       <c r="B40" s="93"/>
       <c r="C40" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D40" s="8">
         <v>0.223</v>
@@ -5428,7 +5440,7 @@
       <c r="A41" s="95"/>
       <c r="B41" s="94"/>
       <c r="C41" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D41" s="27">
         <v>5.8999999999999997E-2</v>
@@ -5455,7 +5467,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D42" s="24">
         <v>6.4000000000000001E-2</v>
@@ -5480,7 +5492,7 @@
       <c r="A43" s="95"/>
       <c r="B43" s="93"/>
       <c r="C43" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D43" s="8">
         <v>2.5000000000000001E-2</v>
@@ -5505,7 +5517,7 @@
       <c r="A44" s="95"/>
       <c r="B44" s="93"/>
       <c r="C44" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D44" s="8">
         <v>4.2000000000000003E-2</v>
@@ -5530,7 +5542,7 @@
       <c r="A45" s="95"/>
       <c r="B45" s="94"/>
       <c r="C45" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D45" s="27">
         <v>3.6999999999999998E-2</v>
@@ -5559,7 +5571,7 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D46" s="24">
         <v>1.5940000000000001</v>
@@ -5572,7 +5584,7 @@
       <c r="A47" s="95"/>
       <c r="B47" s="93"/>
       <c r="C47" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D47" s="8">
         <v>2.7280000000000002</v>
@@ -5585,7 +5597,7 @@
       <c r="A48" s="95"/>
       <c r="B48" s="93"/>
       <c r="C48" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D48" s="33">
         <v>2.44</v>
@@ -5598,7 +5610,7 @@
       <c r="A49" s="95"/>
       <c r="B49" s="94"/>
       <c r="C49" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D49" s="27">
         <v>2.8010000000000002</v>
@@ -5613,7 +5625,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D50" s="34">
         <v>2.75</v>
@@ -5626,7 +5638,7 @@
       <c r="A51" s="95"/>
       <c r="B51" s="93"/>
       <c r="C51" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D51" s="8">
         <v>4.3019999999999996</v>
@@ -5639,7 +5651,7 @@
       <c r="A52" s="95"/>
       <c r="B52" s="93"/>
       <c r="C52" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D52" s="8">
         <v>4.0350000000000001</v>
@@ -5652,13 +5664,13 @@
       <c r="A53" s="95"/>
       <c r="B53" s="94"/>
       <c r="C53" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D53" s="27">
         <v>5.5990000000000002</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -5667,7 +5679,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D54" s="24">
         <v>4.1840000000000002</v>
@@ -5680,7 +5692,7 @@
       <c r="A55" s="95"/>
       <c r="B55" s="93"/>
       <c r="C55" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D55" s="8">
         <v>6.3170000000000002</v>
@@ -5693,7 +5705,7 @@
       <c r="A56" s="95"/>
       <c r="B56" s="93"/>
       <c r="C56" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D56" s="8">
         <v>3.6629999999999998</v>
@@ -5706,7 +5718,7 @@
       <c r="A57" s="95"/>
       <c r="B57" s="94"/>
       <c r="C57" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D57" s="27">
         <v>4.9889999999999999</v>
@@ -5721,7 +5733,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D58" s="24">
         <v>3.4940000000000002</v>
@@ -5734,7 +5746,7 @@
       <c r="A59" s="95"/>
       <c r="B59" s="93"/>
       <c r="C59" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D59" s="8">
         <v>4.5640000000000001</v>
@@ -5747,7 +5759,7 @@
       <c r="A60" s="95"/>
       <c r="B60" s="93"/>
       <c r="C60" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D60" s="8">
         <v>6.5289999999999999</v>
@@ -5760,7 +5772,7 @@
       <c r="A61" s="95"/>
       <c r="B61" s="94"/>
       <c r="C61" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D61" s="27">
         <v>5.649</v>
@@ -5775,7 +5787,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D62" s="24">
         <v>3.5579999999999998</v>
@@ -5788,7 +5800,7 @@
       <c r="A63" s="95"/>
       <c r="B63" s="93"/>
       <c r="C63" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D63" s="8">
         <v>3.3719999999999999</v>
@@ -5801,7 +5813,7 @@
       <c r="A64" s="95"/>
       <c r="B64" s="93"/>
       <c r="C64" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D64" s="8">
         <v>2.1019999999999999</v>
@@ -5814,7 +5826,7 @@
       <c r="A65" s="95"/>
       <c r="B65" s="94"/>
       <c r="C65" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D65" s="27">
         <v>4.5019999999999998</v>
@@ -5829,7 +5841,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="C66" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D66" s="24">
         <v>2.7450000000000001</v>
@@ -5842,7 +5854,7 @@
       <c r="A67" s="95"/>
       <c r="B67" s="93"/>
       <c r="C67" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D67" s="8">
         <v>5.3680000000000003</v>
@@ -5855,7 +5867,7 @@
       <c r="A68" s="95"/>
       <c r="B68" s="93"/>
       <c r="C68" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D68" s="33">
         <v>3.66</v>
@@ -5868,7 +5880,7 @@
       <c r="A69" s="95"/>
       <c r="B69" s="94"/>
       <c r="C69" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D69" s="27">
         <v>6.6040000000000001</v>
@@ -5883,7 +5895,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D70" s="24">
         <v>2.5009999999999999</v>
@@ -5896,7 +5908,7 @@
       <c r="A71" s="95"/>
       <c r="B71" s="93"/>
       <c r="C71" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D71" s="8">
         <v>3.492</v>
@@ -5909,7 +5921,7 @@
       <c r="A72" s="95"/>
       <c r="B72" s="93"/>
       <c r="C72" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D72" s="8">
         <v>3.4239999999999999</v>
@@ -5922,7 +5934,7 @@
       <c r="A73" s="95"/>
       <c r="B73" s="94"/>
       <c r="C73" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D73" s="27">
         <v>4.2069999999999999</v>
@@ -5937,7 +5949,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D74" s="24">
         <v>4.4370000000000003</v>
@@ -5950,7 +5962,7 @@
       <c r="A75" s="95"/>
       <c r="B75" s="93"/>
       <c r="C75" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D75" s="8">
         <v>4.4969999999999999</v>
@@ -5963,7 +5975,7 @@
       <c r="A76" s="95"/>
       <c r="B76" s="93"/>
       <c r="C76" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D76" s="8">
         <v>5.1559999999999997</v>
@@ -5976,7 +5988,7 @@
       <c r="A77" s="95"/>
       <c r="B77" s="94"/>
       <c r="C77" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D77" s="27">
         <v>3.6859999999999999</v>
@@ -5991,7 +6003,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D78" s="24">
         <v>6.9509999999999996</v>
@@ -6004,7 +6016,7 @@
       <c r="A79" s="95"/>
       <c r="B79" s="93"/>
       <c r="C79" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D79" s="8">
         <v>9.1189999999999998</v>
@@ -6017,7 +6029,7 @@
       <c r="A80" s="95"/>
       <c r="B80" s="93"/>
       <c r="C80" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D80" s="8">
         <v>1.0780000000000001</v>
@@ -6030,7 +6042,7 @@
       <c r="A81" s="95"/>
       <c r="B81" s="94"/>
       <c r="C81" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D81" s="27">
         <v>6.0659999999999998</v>
@@ -6045,7 +6057,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D82" s="24">
         <v>1.873</v>
@@ -6058,7 +6070,7 @@
       <c r="A83" s="95"/>
       <c r="B83" s="93"/>
       <c r="C83" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D83" s="8">
         <v>6.8849999999999998</v>
@@ -6071,7 +6083,7 @@
       <c r="A84" s="95"/>
       <c r="B84" s="93"/>
       <c r="C84" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D84" s="8">
         <v>2.2909999999999999</v>
@@ -6084,7 +6096,7 @@
       <c r="A85" s="95"/>
       <c r="B85" s="94"/>
       <c r="C85" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D85" s="27">
         <v>5.2519999999999998</v>
@@ -6099,7 +6111,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D86" s="24">
         <v>5.5759999999999996</v>
@@ -6112,7 +6124,7 @@
       <c r="A87" s="95"/>
       <c r="B87" s="93"/>
       <c r="C87" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D87" s="8">
         <v>6.0880000000000001</v>
@@ -6125,7 +6137,7 @@
       <c r="A88" s="95"/>
       <c r="B88" s="93"/>
       <c r="C88" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D88" s="33">
         <v>7.76</v>
@@ -6138,7 +6150,7 @@
       <c r="A89" s="95"/>
       <c r="B89" s="94"/>
       <c r="C89" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D89" s="35">
         <v>7.2</v>
@@ -6149,13 +6161,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="95" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B90" s="92">
         <v>9.8097434965383901</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D90" s="24">
         <v>3.8759999999999999</v>
@@ -6168,7 +6180,7 @@
       <c r="A91" s="95"/>
       <c r="B91" s="93"/>
       <c r="C91" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D91" s="8">
         <v>5.0739999999999998</v>
@@ -6181,7 +6193,7 @@
       <c r="A92" s="95"/>
       <c r="B92" s="93"/>
       <c r="C92" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D92" s="33">
         <v>5.38</v>
@@ -6194,7 +6206,7 @@
       <c r="A93" s="95"/>
       <c r="B93" s="94"/>
       <c r="C93" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D93" s="27">
         <v>5.8310000000000004</v>
@@ -6209,7 +6221,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D94" s="24">
         <v>3.536</v>
@@ -6222,7 +6234,7 @@
       <c r="A95" s="95"/>
       <c r="B95" s="93"/>
       <c r="C95" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D95" s="8">
         <v>3.411</v>
@@ -6235,7 +6247,7 @@
       <c r="A96" s="95"/>
       <c r="B96" s="93"/>
       <c r="C96" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D96" s="8">
         <v>3.5379999999999998</v>
@@ -6248,7 +6260,7 @@
       <c r="A97" s="95"/>
       <c r="B97" s="94"/>
       <c r="C97" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D97" s="35">
         <v>1.55</v>
@@ -6263,7 +6275,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D98" s="34">
         <v>4.57</v>
@@ -6276,7 +6288,7 @@
       <c r="A99" s="95"/>
       <c r="B99" s="93"/>
       <c r="C99" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D99" s="33">
         <v>4.03</v>
@@ -6289,7 +6301,7 @@
       <c r="A100" s="95"/>
       <c r="B100" s="93"/>
       <c r="C100" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D100" s="8">
         <v>4.9420000000000002</v>
@@ -6302,7 +6314,7 @@
       <c r="A101" s="95"/>
       <c r="B101" s="94"/>
       <c r="C101" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D101" s="27">
         <v>5.008</v>
@@ -6317,7 +6329,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="C102" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D102" s="24">
         <v>5.3049999999999997</v>
@@ -6330,7 +6342,7 @@
       <c r="A103" s="95"/>
       <c r="B103" s="93"/>
       <c r="C103" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D103" s="8">
         <v>5.1749999999999998</v>
@@ -6343,7 +6355,7 @@
       <c r="A104" s="95"/>
       <c r="B104" s="93"/>
       <c r="C104" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D104" s="33">
         <v>3.8</v>
@@ -6356,7 +6368,7 @@
       <c r="A105" s="95"/>
       <c r="B105" s="94"/>
       <c r="C105" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D105" s="27">
         <v>2.0289999999999999</v>
@@ -6371,7 +6383,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="C106" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D106" s="24">
         <v>5.7249999999999996</v>
@@ -6384,7 +6396,7 @@
       <c r="A107" s="95"/>
       <c r="B107" s="93"/>
       <c r="C107" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D107" s="8">
         <v>4.7889999999999997</v>
@@ -6397,7 +6409,7 @@
       <c r="A108" s="95"/>
       <c r="B108" s="93"/>
       <c r="C108" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D108" s="8">
         <v>4.2969999999999997</v>
@@ -6410,7 +6422,7 @@
       <c r="A109" s="95"/>
       <c r="B109" s="94"/>
       <c r="C109" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D109" s="27">
         <v>4.6429999999999998</v>
@@ -6425,7 +6437,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="C110" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D110" s="24">
         <v>5.109</v>
@@ -6438,7 +6450,7 @@
       <c r="A111" s="95"/>
       <c r="B111" s="93"/>
       <c r="C111" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D111" s="8">
         <v>4.1719999999999997</v>
@@ -6451,7 +6463,7 @@
       <c r="A112" s="95"/>
       <c r="B112" s="93"/>
       <c r="C112" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D112" s="8">
         <v>4.9649999999999999</v>
@@ -6464,7 +6476,7 @@
       <c r="A113" s="95"/>
       <c r="B113" s="94"/>
       <c r="C113" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D113" s="27">
         <v>4.7190000000000003</v>
@@ -6479,7 +6491,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="C114" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D114" s="24">
         <v>4.2229999999999999</v>
@@ -6492,7 +6504,7 @@
       <c r="A115" s="95"/>
       <c r="B115" s="93"/>
       <c r="C115" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D115" s="8">
         <v>3.113</v>
@@ -6505,7 +6517,7 @@
       <c r="A116" s="95"/>
       <c r="B116" s="93"/>
       <c r="C116" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D116" s="8">
         <v>5.5949999999999998</v>
@@ -6518,7 +6530,7 @@
       <c r="A117" s="95"/>
       <c r="B117" s="94"/>
       <c r="C117" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D117" s="27">
         <v>5.1429999999999998</v>
@@ -6533,7 +6545,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="C118" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D118" s="24">
         <v>7.8550000000000004</v>
@@ -6546,7 +6558,7 @@
       <c r="A119" s="95"/>
       <c r="B119" s="93"/>
       <c r="C119" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D119" s="8">
         <v>6.9480000000000004</v>
@@ -6559,7 +6571,7 @@
       <c r="A120" s="95"/>
       <c r="B120" s="93"/>
       <c r="C120" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D120" s="8">
         <v>7.1459999999999999</v>
@@ -6572,7 +6584,7 @@
       <c r="A121" s="95"/>
       <c r="B121" s="94"/>
       <c r="C121" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D121" s="27">
         <v>6.9640000000000004</v>
@@ -6587,7 +6599,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="C122" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D122" s="24">
         <v>3.496</v>
@@ -6600,7 +6612,7 @@
       <c r="A123" s="95"/>
       <c r="B123" s="93"/>
       <c r="C123" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D123" s="8">
         <v>6.2430000000000003</v>
@@ -6613,7 +6625,7 @@
       <c r="A124" s="95"/>
       <c r="B124" s="93"/>
       <c r="C124" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D124" s="33">
         <v>1.85</v>
@@ -6626,7 +6638,7 @@
       <c r="A125" s="95"/>
       <c r="B125" s="94"/>
       <c r="C125" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D125" s="27">
         <v>5.5670000000000002</v>
@@ -6641,7 +6653,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="C126" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D126" s="34">
         <v>5</v>
@@ -6654,7 +6666,7 @@
       <c r="A127" s="95"/>
       <c r="B127" s="93"/>
       <c r="C127" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D127" s="33">
         <v>4.72</v>
@@ -6667,7 +6679,7 @@
       <c r="A128" s="95"/>
       <c r="B128" s="93"/>
       <c r="C128" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D128" s="8">
         <v>5.056</v>
@@ -6680,7 +6692,7 @@
       <c r="A129" s="95"/>
       <c r="B129" s="94"/>
       <c r="C129" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D129" s="27">
         <v>4.9589999999999996</v>
@@ -6695,7 +6707,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="C130" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D130" s="24">
         <v>3.5379999999999998</v>
@@ -6708,7 +6720,7 @@
       <c r="A131" s="95"/>
       <c r="B131" s="93"/>
       <c r="C131" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D131" s="8">
         <v>5.5570000000000004</v>
@@ -6721,7 +6733,7 @@
       <c r="A132" s="95"/>
       <c r="B132" s="93"/>
       <c r="C132" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D132" s="8">
         <v>4.2789999999999999</v>
@@ -6734,7 +6746,7 @@
       <c r="A133" s="95"/>
       <c r="B133" s="94"/>
       <c r="C133" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D133" s="27">
         <v>5.923</v>
@@ -6751,7 +6763,7 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="C134" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D134" s="24">
         <v>98.843000000000004</v>
@@ -6764,7 +6776,7 @@
       <c r="A135" s="95"/>
       <c r="B135" s="93"/>
       <c r="C135" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D135" s="8">
         <v>128.57499999999999</v>
@@ -6777,7 +6789,7 @@
       <c r="A136" s="95"/>
       <c r="B136" s="93"/>
       <c r="C136" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D136" s="8">
         <v>97.275999999999996</v>
@@ -6790,7 +6802,7 @@
       <c r="A137" s="95"/>
       <c r="B137" s="94"/>
       <c r="C137" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D137" s="27">
         <v>110.58799999999999</v>
@@ -6805,7 +6817,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="C138" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D138" s="24">
         <v>105.631</v>
@@ -6818,7 +6830,7 @@
       <c r="A139" s="95"/>
       <c r="B139" s="93"/>
       <c r="C139" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D139" s="8">
         <v>144.63300000000001</v>
@@ -6831,7 +6843,7 @@
       <c r="A140" s="95"/>
       <c r="B140" s="93"/>
       <c r="C140" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D140" s="8">
         <v>102.96899999999999</v>
@@ -6844,13 +6856,13 @@
       <c r="A141" s="95"/>
       <c r="B141" s="94"/>
       <c r="C141" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D141" s="27">
         <v>89.209000000000003</v>
       </c>
       <c r="E141" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -6859,7 +6871,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="C142" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D142" s="24">
         <v>116.535</v>
@@ -6872,7 +6884,7 @@
       <c r="A143" s="95"/>
       <c r="B143" s="93"/>
       <c r="C143" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D143" s="8">
         <v>114.30200000000001</v>
@@ -6885,7 +6897,7 @@
       <c r="A144" s="95"/>
       <c r="B144" s="93"/>
       <c r="C144" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D144" s="8">
         <v>111.169</v>
@@ -6898,7 +6910,7 @@
       <c r="A145" s="95"/>
       <c r="B145" s="94"/>
       <c r="C145" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D145" s="27">
         <v>120.961</v>
@@ -6913,7 +6925,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="C146" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D146" s="24">
         <v>106.83499999999999</v>
@@ -6926,7 +6938,7 @@
       <c r="A147" s="95"/>
       <c r="B147" s="93"/>
       <c r="C147" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D147" s="33">
         <v>112.41</v>
@@ -6939,7 +6951,7 @@
       <c r="A148" s="95"/>
       <c r="B148" s="93"/>
       <c r="C148" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D148" s="8">
         <v>107.163</v>
@@ -6952,7 +6964,7 @@
       <c r="A149" s="95"/>
       <c r="B149" s="94"/>
       <c r="C149" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D149" s="27">
         <v>77.367999999999995</v>
@@ -6967,7 +6979,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="C150" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D150" s="24">
         <v>117.45099999999999</v>
@@ -6980,7 +6992,7 @@
       <c r="A151" s="95"/>
       <c r="B151" s="93"/>
       <c r="C151" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D151" s="8">
         <v>110.10599999999999</v>
@@ -6993,7 +7005,7 @@
       <c r="A152" s="95"/>
       <c r="B152" s="93"/>
       <c r="C152" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D152" s="8">
         <v>125.364</v>
@@ -7006,7 +7018,7 @@
       <c r="A153" s="95"/>
       <c r="B153" s="94"/>
       <c r="C153" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D153" s="27">
         <v>132.74700000000001</v>
@@ -7021,7 +7033,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="C154" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D154" s="24">
         <v>118.60299999999999</v>
@@ -7034,7 +7046,7 @@
       <c r="A155" s="95"/>
       <c r="B155" s="93"/>
       <c r="C155" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D155" s="8">
         <v>113.134</v>
@@ -7047,7 +7059,7 @@
       <c r="A156" s="95"/>
       <c r="B156" s="93"/>
       <c r="C156" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D156" s="8">
         <v>101.70699999999999</v>
@@ -7060,7 +7072,7 @@
       <c r="A157" s="95"/>
       <c r="B157" s="94"/>
       <c r="C157" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D157" s="27">
         <v>115.34699999999999</v>
@@ -7075,7 +7087,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="C158" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D158" s="24">
         <v>119.44499999999999</v>
@@ -7088,7 +7100,7 @@
       <c r="A159" s="95"/>
       <c r="B159" s="93"/>
       <c r="C159" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D159" s="8">
         <v>115.79600000000001</v>
@@ -7101,7 +7113,7 @@
       <c r="A160" s="95"/>
       <c r="B160" s="93"/>
       <c r="C160" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D160" s="8">
         <v>104.441</v>
@@ -7114,7 +7126,7 @@
       <c r="A161" s="95"/>
       <c r="B161" s="94"/>
       <c r="C161" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D161" s="27">
         <v>114.58499999999999</v>
@@ -7129,7 +7141,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="C162" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D162" s="24">
         <v>93.126999999999995</v>
@@ -7142,7 +7154,7 @@
       <c r="A163" s="95"/>
       <c r="B163" s="93"/>
       <c r="C163" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D163" s="8">
         <v>90.147000000000006</v>
@@ -7155,7 +7167,7 @@
       <c r="A164" s="95"/>
       <c r="B164" s="93"/>
       <c r="C164" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D164" s="8">
         <v>100.10299999999999</v>
@@ -7168,7 +7180,7 @@
       <c r="A165" s="95"/>
       <c r="B165" s="94"/>
       <c r="C165" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D165" s="27">
         <v>90.888000000000005</v>
@@ -7183,7 +7195,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="C166" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D166" s="24">
         <v>93.251000000000005</v>
@@ -7196,7 +7208,7 @@
       <c r="A167" s="95"/>
       <c r="B167" s="93"/>
       <c r="C167" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D167" s="8">
         <v>119.989</v>
@@ -7209,26 +7221,26 @@
       <c r="A168" s="95"/>
       <c r="B168" s="93"/>
       <c r="C168" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E168" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="95"/>
       <c r="B169" s="94"/>
       <c r="C169" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D169" s="27">
         <v>85.850999999999999</v>
       </c>
       <c r="E169" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -7237,7 +7249,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="C170" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D170" s="24">
         <v>118.374</v>
@@ -7250,7 +7262,7 @@
       <c r="A171" s="95"/>
       <c r="B171" s="93"/>
       <c r="C171" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D171" s="8">
         <v>116.499</v>
@@ -7263,7 +7275,7 @@
       <c r="A172" s="95"/>
       <c r="B172" s="93"/>
       <c r="C172" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D172" s="8">
         <v>100.455</v>
@@ -7276,7 +7288,7 @@
       <c r="A173" s="95"/>
       <c r="B173" s="94"/>
       <c r="C173" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D173" s="27">
         <v>113.902</v>
@@ -7291,7 +7303,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="C174" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D174" s="24">
         <v>79.016000000000005</v>
@@ -7304,7 +7316,7 @@
       <c r="A175" s="95"/>
       <c r="B175" s="93"/>
       <c r="C175" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D175" s="8">
         <v>125.178</v>
@@ -7317,7 +7329,7 @@
       <c r="A176" s="95"/>
       <c r="B176" s="93"/>
       <c r="C176" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D176" s="8">
         <v>132.01400000000001</v>
@@ -7330,7 +7342,7 @@
       <c r="A177" s="95"/>
       <c r="B177" s="94"/>
       <c r="C177" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D177" s="35">
         <v>108.12</v>
@@ -7347,7 +7359,7 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="C178" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D178" s="34">
         <v>0.4</v>
@@ -7360,7 +7372,7 @@
       <c r="A179" s="95"/>
       <c r="B179" s="93"/>
       <c r="C179" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D179" s="8">
         <v>0.111</v>
@@ -7373,7 +7385,7 @@
       <c r="A180" s="95"/>
       <c r="B180" s="93"/>
       <c r="C180" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D180" s="33">
         <v>0.25</v>
@@ -7386,7 +7398,7 @@
       <c r="A181" s="95"/>
       <c r="B181" s="94"/>
       <c r="C181" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D181" s="35">
         <v>0</v>
@@ -7401,7 +7413,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="C182" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D182" s="24">
         <v>0.121</v>
@@ -7414,7 +7426,7 @@
       <c r="A183" s="95"/>
       <c r="B183" s="93"/>
       <c r="C183" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D183" s="8">
         <v>0.158</v>
@@ -7427,7 +7439,7 @@
       <c r="A184" s="95"/>
       <c r="B184" s="93"/>
       <c r="C184" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D184" s="8">
         <v>0.222</v>
@@ -7440,7 +7452,7 @@
       <c r="A185" s="95"/>
       <c r="B185" s="94"/>
       <c r="C185" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D185" s="35">
         <v>0.5</v>
@@ -7455,7 +7467,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="C186" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D186" s="24">
         <v>9.8000000000000004E-2</v>
@@ -7468,7 +7480,7 @@
       <c r="A187" s="95"/>
       <c r="B187" s="93"/>
       <c r="C187" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D187" s="8">
         <v>0.128</v>
@@ -7481,7 +7493,7 @@
       <c r="A188" s="95"/>
       <c r="B188" s="93"/>
       <c r="C188" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D188" s="8">
         <v>8.5000000000000006E-2</v>
@@ -7494,7 +7506,7 @@
       <c r="A189" s="95"/>
       <c r="B189" s="94"/>
       <c r="C189" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D189" s="27">
         <v>7.9000000000000001E-2</v>
@@ -7509,7 +7521,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="C190" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D190" s="24">
         <v>0.108</v>
@@ -7522,7 +7534,7 @@
       <c r="A191" s="95"/>
       <c r="B191" s="93"/>
       <c r="C191" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D191" s="8">
         <v>0</v>
@@ -7535,7 +7547,7 @@
       <c r="A192" s="95"/>
       <c r="B192" s="93"/>
       <c r="C192" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D192" s="8">
         <v>0.44400000000000001</v>
@@ -7548,7 +7560,7 @@
       <c r="A193" s="95"/>
       <c r="B193" s="94"/>
       <c r="C193" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D193" s="35">
         <v>0.7</v>
@@ -7563,7 +7575,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="C194" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D194" s="24">
         <v>8.7999999999999995E-2</v>
@@ -7576,7 +7588,7 @@
       <c r="A195" s="95"/>
       <c r="B195" s="93"/>
       <c r="C195" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D195" s="8">
         <v>0.107</v>
@@ -7589,7 +7601,7 @@
       <c r="A196" s="95"/>
       <c r="B196" s="93"/>
       <c r="C196" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D196" s="8">
         <v>0.39400000000000002</v>
@@ -7602,7 +7614,7 @@
       <c r="A197" s="95"/>
       <c r="B197" s="94"/>
       <c r="C197" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D197" s="27">
         <v>0.16700000000000001</v>
@@ -7617,7 +7629,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="C198" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D198" s="24">
         <v>4.3999999999999997E-2</v>
@@ -7630,7 +7642,7 @@
       <c r="A199" s="95"/>
       <c r="B199" s="93"/>
       <c r="C199" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D199" s="8">
         <v>0.16200000000000001</v>
@@ -7643,7 +7655,7 @@
       <c r="A200" s="95"/>
       <c r="B200" s="93"/>
       <c r="C200" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D200" s="8">
         <v>0.17399999999999999</v>
@@ -7656,7 +7668,7 @@
       <c r="A201" s="95"/>
       <c r="B201" s="94"/>
       <c r="C201" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D201" s="27">
         <v>2.4E-2</v>
@@ -7671,7 +7683,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="C202" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D202" s="24">
         <v>0.23100000000000001</v>
@@ -7684,7 +7696,7 @@
       <c r="A203" s="95"/>
       <c r="B203" s="93"/>
       <c r="C203" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D203" s="33">
         <v>0.25</v>
@@ -7697,7 +7709,7 @@
       <c r="A204" s="95"/>
       <c r="B204" s="93"/>
       <c r="C204" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D204" s="8">
         <v>0.13200000000000001</v>
@@ -7710,7 +7722,7 @@
       <c r="A205" s="95"/>
       <c r="B205" s="94"/>
       <c r="C205" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D205" s="27">
         <v>0.13300000000000001</v>
@@ -7725,7 +7737,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="C206" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D206" s="24">
         <v>0.182</v>
@@ -7738,7 +7750,7 @@
       <c r="A207" s="95"/>
       <c r="B207" s="93"/>
       <c r="C207" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D207" s="8">
         <v>7.3999999999999996E-2</v>
@@ -7751,7 +7763,7 @@
       <c r="A208" s="95"/>
       <c r="B208" s="93"/>
       <c r="C208" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D208" s="8">
         <v>0.13600000000000001</v>
@@ -7764,7 +7776,7 @@
       <c r="A209" s="95"/>
       <c r="B209" s="94"/>
       <c r="C209" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D209" s="27">
         <v>6.5000000000000002E-2</v>
@@ -7779,7 +7791,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="C210" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D210" s="24">
         <v>0.38500000000000001</v>
@@ -7792,7 +7804,7 @@
       <c r="A211" s="95"/>
       <c r="B211" s="93"/>
       <c r="C211" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D211" s="8">
         <v>0</v>
@@ -7805,7 +7817,7 @@
       <c r="A212" s="95"/>
       <c r="B212" s="93"/>
       <c r="C212" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D212" s="8">
         <v>0.66700000000000004</v>
@@ -7818,7 +7830,7 @@
       <c r="A213" s="95"/>
       <c r="B213" s="94"/>
       <c r="C213" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D213" s="35">
         <v>0.25</v>
@@ -7833,7 +7845,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="C214" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D214" s="24">
         <v>0.152</v>
@@ -7846,7 +7858,7 @@
       <c r="A215" s="95"/>
       <c r="B215" s="93"/>
       <c r="C215" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D215" s="8">
         <v>8.5999999999999993E-2</v>
@@ -7859,7 +7871,7 @@
       <c r="A216" s="95"/>
       <c r="B216" s="93"/>
       <c r="C216" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D216" s="8">
         <v>0.17100000000000001</v>
@@ -7872,7 +7884,7 @@
       <c r="A217" s="95"/>
       <c r="B217" s="94"/>
       <c r="C217" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D217" s="27">
         <v>0.188</v>
@@ -7887,7 +7899,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="C218" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D218" s="24">
         <v>0.26700000000000002</v>
@@ -7900,7 +7912,7 @@
       <c r="A219" s="95"/>
       <c r="B219" s="93"/>
       <c r="C219" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D219" s="8">
         <v>0.33300000000000002</v>
@@ -7913,7 +7925,7 @@
       <c r="A220" s="95"/>
       <c r="B220" s="93"/>
       <c r="C220" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D220" s="8">
         <v>0.21099999999999999</v>
@@ -7926,7 +7938,7 @@
       <c r="A221" s="95"/>
       <c r="B221" s="94"/>
       <c r="C221" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D221" s="27">
         <v>7.6999999999999999E-2</v>
@@ -7943,33 +7955,33 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="C222" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D222" s="24">
         <v>30.606000000000002</v>
       </c>
       <c r="E222" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="95"/>
       <c r="B223" s="93"/>
       <c r="C223" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E223" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="95"/>
       <c r="B224" s="93"/>
       <c r="C224" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D224" s="8">
         <v>65.313999999999993</v>
@@ -7982,13 +7994,13 @@
       <c r="A225" s="95"/>
       <c r="B225" s="94"/>
       <c r="C225" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D225" s="27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E225" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -7997,33 +8009,33 @@
         <v>13.289870274379901</v>
       </c>
       <c r="C226" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D226" s="24">
         <v>25.603000000000002</v>
       </c>
       <c r="E226" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="95"/>
       <c r="B227" s="93"/>
       <c r="C227" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D227" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E227" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="95"/>
       <c r="B228" s="93"/>
       <c r="C228" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D228" s="8">
         <v>30.105</v>
@@ -8036,13 +8048,13 @@
       <c r="A229" s="95"/>
       <c r="B229" s="94"/>
       <c r="C229" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D229" s="35">
         <v>1</v>
       </c>
       <c r="E229" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -8051,7 +8063,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="C230" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D230" s="24">
         <v>42.305</v>
@@ -8064,20 +8076,20 @@
       <c r="A231" s="95"/>
       <c r="B231" s="93"/>
       <c r="C231" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D231" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E231" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="95"/>
       <c r="B232" s="93"/>
       <c r="C232" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D232" s="8">
         <v>62.072000000000003</v>
@@ -8090,7 +8102,7 @@
       <c r="A233" s="95"/>
       <c r="B233" s="94"/>
       <c r="C233" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D233" s="27">
         <v>18.776</v>
@@ -8105,7 +8117,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="C234" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D234" s="24">
         <v>52.161000000000001</v>
@@ -8118,7 +8130,7 @@
       <c r="A235" s="95"/>
       <c r="B235" s="93"/>
       <c r="C235" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D235" s="8">
         <v>26.923999999999999</v>
@@ -8131,7 +8143,7 @@
       <c r="A236" s="95"/>
       <c r="B236" s="93"/>
       <c r="C236" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D236" s="8">
         <v>50.886000000000003</v>
@@ -8144,13 +8156,13 @@
       <c r="A237" s="95"/>
       <c r="B237" s="94"/>
       <c r="C237" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D237" s="27">
         <v>21</v>
       </c>
       <c r="E237" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -8159,7 +8171,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="C238" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D238" s="24">
         <v>59.816000000000003</v>
@@ -8172,7 +8184,7 @@
       <c r="A239" s="95"/>
       <c r="B239" s="93"/>
       <c r="C239" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D239" s="8">
         <v>29.937000000000001</v>
@@ -8185,7 +8197,7 @@
       <c r="A240" s="95"/>
       <c r="B240" s="93"/>
       <c r="C240" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D240" s="8">
         <v>54.695</v>
@@ -8198,13 +8210,13 @@
       <c r="A241" s="95"/>
       <c r="B241" s="94"/>
       <c r="C241" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D241" s="27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E241" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -8213,33 +8225,33 @@
         <v>11.191736578258899</v>
       </c>
       <c r="C242" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D242" s="34">
         <v>8</v>
       </c>
       <c r="E242" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="95"/>
       <c r="B243" s="93"/>
       <c r="C243" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D243" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E243" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="95"/>
       <c r="B244" s="93"/>
       <c r="C244" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D244" s="8">
         <v>47.963000000000001</v>
@@ -8252,13 +8264,13 @@
       <c r="A245" s="95"/>
       <c r="B245" s="94"/>
       <c r="C245" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D245" s="27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E245" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -8267,33 +8279,33 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="C246" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D246" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E246" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="95"/>
       <c r="B247" s="93"/>
       <c r="C247" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D247" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E247" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="95"/>
       <c r="B248" s="93"/>
       <c r="C248" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D248" s="8">
         <v>62.637</v>
@@ -8306,7 +8318,7 @@
       <c r="A249" s="95"/>
       <c r="B249" s="94"/>
       <c r="C249" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D249" s="27">
         <v>29.684000000000001</v>
@@ -8321,7 +8333,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="C250" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D250" s="24">
         <v>55.052999999999997</v>
@@ -8334,7 +8346,7 @@
       <c r="A251" s="95"/>
       <c r="B251" s="93"/>
       <c r="C251" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D251" s="8">
         <v>31.234999999999999</v>
@@ -8347,7 +8359,7 @@
       <c r="A252" s="95"/>
       <c r="B252" s="93"/>
       <c r="C252" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D252" s="8">
         <v>52.920999999999999</v>
@@ -8360,7 +8372,7 @@
       <c r="A253" s="95"/>
       <c r="B253" s="94"/>
       <c r="C253" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D253" s="35">
         <v>16.149999999999999</v>
@@ -8375,7 +8387,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="C254" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D254" s="24">
         <v>26.276</v>
@@ -8388,39 +8400,39 @@
       <c r="A255" s="95"/>
       <c r="B255" s="93"/>
       <c r="C255" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D255" s="33">
         <v>1</v>
       </c>
       <c r="E255" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="95"/>
       <c r="B256" s="93"/>
       <c r="C256" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E256" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="95"/>
       <c r="B257" s="94"/>
       <c r="C257" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D257" s="35">
         <v>25</v>
       </c>
       <c r="E257" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -8429,7 +8441,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="C258" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D258" s="24">
         <v>42.719000000000001</v>
@@ -8442,20 +8454,20 @@
       <c r="A259" s="95"/>
       <c r="B259" s="93"/>
       <c r="C259" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E259" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="95"/>
       <c r="B260" s="93"/>
       <c r="C260" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D260" s="8">
         <v>75.963999999999999</v>
@@ -8468,7 +8480,7 @@
       <c r="A261" s="95"/>
       <c r="B261" s="94"/>
       <c r="C261" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D261" s="27">
         <v>6.6669999999999998</v>
@@ -8483,7 +8495,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="C262" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D262" s="24">
         <v>34.405000000000001</v>
@@ -8496,20 +8508,20 @@
       <c r="A263" s="95"/>
       <c r="B263" s="93"/>
       <c r="C263" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E263" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="95"/>
       <c r="B264" s="93"/>
       <c r="C264" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D264" s="8">
         <v>49.311999999999998</v>
@@ -8522,7 +8534,7 @@
       <c r="A265" s="95"/>
       <c r="B265" s="94"/>
       <c r="C265" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D265" s="35">
         <v>7.2</v>
@@ -8539,33 +8551,33 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="C266" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D266" s="34">
         <v>36</v>
       </c>
       <c r="E266" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="95"/>
       <c r="B267" s="93"/>
       <c r="C267" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D267" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E267" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="95"/>
       <c r="B268" s="93"/>
       <c r="C268" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D268" s="33">
         <v>46.25</v>
@@ -8578,13 +8590,13 @@
       <c r="A269" s="95"/>
       <c r="B269" s="94"/>
       <c r="C269" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D269" s="27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E269" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -8593,7 +8605,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="C270" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D270" s="34">
         <v>43.5</v>
@@ -8606,20 +8618,20 @@
       <c r="A271" s="95"/>
       <c r="B271" s="93"/>
       <c r="C271" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D271" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E271" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="95"/>
       <c r="B272" s="93"/>
       <c r="C272" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D272" s="33">
         <v>46</v>
@@ -8632,13 +8644,13 @@
       <c r="A273" s="95"/>
       <c r="B273" s="94"/>
       <c r="C273" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D273" s="35">
         <v>47</v>
       </c>
       <c r="E273" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -8647,33 +8659,33 @@
         <v>10.670492424171201</v>
       </c>
       <c r="C274" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D274" s="34">
         <v>66</v>
       </c>
       <c r="E274" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="95"/>
       <c r="B275" s="93"/>
       <c r="C275" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D275" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E275" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="95"/>
       <c r="B276" s="93"/>
       <c r="C276" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D276" s="8">
         <v>40.332999999999998</v>
@@ -8686,7 +8698,7 @@
       <c r="A277" s="95"/>
       <c r="B277" s="94"/>
       <c r="C277" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D277" s="35">
         <v>47.6</v>
@@ -8701,7 +8713,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="C278" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D278" s="24">
         <v>39.438000000000002</v>
@@ -8714,7 +8726,7 @@
       <c r="A279" s="95"/>
       <c r="B279" s="93"/>
       <c r="C279" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D279" s="8">
         <v>48.625</v>
@@ -8727,7 +8739,7 @@
       <c r="A280" s="95"/>
       <c r="B280" s="93"/>
       <c r="C280" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D280" s="33">
         <v>41</v>
@@ -8740,13 +8752,13 @@
       <c r="A281" s="95"/>
       <c r="B281" s="94"/>
       <c r="C281" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D281" s="35">
         <v>35</v>
       </c>
       <c r="E281" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -8755,7 +8767,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="C282" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D282" s="24">
         <v>37.555999999999997</v>
@@ -8768,7 +8780,7 @@
       <c r="A283" s="95"/>
       <c r="B283" s="93"/>
       <c r="C283" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D283" s="33">
         <v>39.5</v>
@@ -8781,7 +8793,7 @@
       <c r="A284" s="95"/>
       <c r="B284" s="93"/>
       <c r="C284" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D284" s="33">
         <v>42</v>
@@ -8794,13 +8806,13 @@
       <c r="A285" s="95"/>
       <c r="B285" s="94"/>
       <c r="C285" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D285" s="27">
         <v>49</v>
       </c>
       <c r="E285" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -8809,7 +8821,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="C286" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D286" s="34">
         <v>53.5</v>
@@ -8822,20 +8834,20 @@
       <c r="A287" s="95"/>
       <c r="B287" s="93"/>
       <c r="C287" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E287" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="288" spans="1:5">
       <c r="A288" s="95"/>
       <c r="B288" s="93"/>
       <c r="C288" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D288" s="8">
         <v>46.143000000000001</v>
@@ -8848,13 +8860,13 @@
       <c r="A289" s="95"/>
       <c r="B289" s="94"/>
       <c r="C289" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D289" s="27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E289" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -8863,33 +8875,33 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="C290" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D290" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E290" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="291" spans="1:5">
       <c r="A291" s="95"/>
       <c r="B291" s="93"/>
       <c r="C291" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D291" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E291" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="292" spans="1:5">
       <c r="A292" s="95"/>
       <c r="B292" s="93"/>
       <c r="C292" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D292" s="8">
         <v>44.713999999999999</v>
@@ -8902,7 +8914,7 @@
       <c r="A293" s="95"/>
       <c r="B293" s="94"/>
       <c r="C293" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D293" s="35">
         <v>48</v>
@@ -8917,7 +8929,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="C294" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D294" s="24">
         <v>38.478000000000002</v>
@@ -8930,7 +8942,7 @@
       <c r="A295" s="95"/>
       <c r="B295" s="93"/>
       <c r="C295" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D295" s="8">
         <v>40.125</v>
@@ -8943,7 +8955,7 @@
       <c r="A296" s="95"/>
       <c r="B296" s="93"/>
       <c r="C296" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D296" s="8">
         <v>34.064999999999998</v>
@@ -8956,7 +8968,7 @@
       <c r="A297" s="95"/>
       <c r="B297" s="94"/>
       <c r="C297" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D297" s="27">
         <v>43.286000000000001</v>
@@ -8971,7 +8983,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="C298" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D298" s="34">
         <v>44.7</v>
@@ -8984,39 +8996,39 @@
       <c r="A299" s="95"/>
       <c r="B299" s="93"/>
       <c r="C299" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D299" s="33">
         <v>41</v>
       </c>
       <c r="E299" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="300" spans="1:5">
       <c r="A300" s="95"/>
       <c r="B300" s="93"/>
       <c r="C300" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D300" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E300" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="301" spans="1:5">
       <c r="A301" s="95"/>
       <c r="B301" s="94"/>
       <c r="C301" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D301" s="35">
         <v>52</v>
       </c>
       <c r="E301" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -9025,33 +9037,33 @@
         <v>11.139438061733999</v>
       </c>
       <c r="C302" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D302" s="34">
         <v>35</v>
       </c>
       <c r="E302" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="303" spans="1:5">
       <c r="A303" s="95"/>
       <c r="B303" s="93"/>
       <c r="C303" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D303" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E303" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="304" spans="1:5">
       <c r="A304" s="95"/>
       <c r="B304" s="93"/>
       <c r="C304" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D304" s="8">
         <v>41.667000000000002</v>
@@ -9064,7 +9076,7 @@
       <c r="A305" s="95"/>
       <c r="B305" s="94"/>
       <c r="C305" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D305" s="35">
         <v>44</v>
@@ -9079,7 +9091,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="C306" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D306" s="24">
         <v>47.832999999999998</v>
@@ -9092,20 +9104,20 @@
       <c r="A307" s="95"/>
       <c r="B307" s="93"/>
       <c r="C307" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D307" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E307" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="308" spans="1:5">
       <c r="A308" s="95"/>
       <c r="B308" s="93"/>
       <c r="C308" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D308" s="33">
         <v>43</v>
@@ -9118,7 +9130,7 @@
       <c r="A309" s="95"/>
       <c r="B309" s="94"/>
       <c r="C309" s="8" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D309" s="8">
         <v>47.332999999999998</v>
@@ -9129,13 +9141,13 @@
     </row>
     <row r="310" spans="1:5">
       <c r="A310" s="95" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B310" s="92">
         <v>9.8097434965383901</v>
       </c>
       <c r="C310" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D310" s="34">
         <v>0.05</v>
@@ -9148,20 +9160,20 @@
       <c r="A311" s="95"/>
       <c r="B311" s="93"/>
       <c r="C311" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D311" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E311" s="37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="312" spans="1:5">
       <c r="A312" s="95"/>
       <c r="B312" s="93"/>
       <c r="C312" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D312" s="33">
         <v>0.2</v>
@@ -9174,7 +9186,7 @@
       <c r="A313" s="95"/>
       <c r="B313" s="94"/>
       <c r="C313" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D313" s="35">
         <v>0</v>
@@ -9189,7 +9201,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="C314" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D314" s="34">
         <v>6.0606E-2</v>
@@ -9202,20 +9214,20 @@
       <c r="A315" s="95"/>
       <c r="B315" s="93"/>
       <c r="C315" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D315" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E315" s="37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="316" spans="1:5">
       <c r="A316" s="95"/>
       <c r="B316" s="93"/>
       <c r="C316" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D316" s="33">
         <v>0.33333299999999999</v>
@@ -9228,7 +9240,7 @@
       <c r="A317" s="95"/>
       <c r="B317" s="94"/>
       <c r="C317" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D317" s="35">
         <v>0.25</v>
@@ -9243,7 +9255,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="C318" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D318" s="34">
         <v>2.4389999999999998E-2</v>
@@ -9256,20 +9268,20 @@
       <c r="A319" s="95"/>
       <c r="B319" s="93"/>
       <c r="C319" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D319" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E319" s="37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="320" spans="1:5">
       <c r="A320" s="95"/>
       <c r="B320" s="93"/>
       <c r="C320" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D320" s="33">
         <v>0.1875</v>
@@ -9282,7 +9294,7 @@
       <c r="A321" s="95"/>
       <c r="B321" s="94"/>
       <c r="C321" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D321" s="35">
         <v>0.13513500000000001</v>
@@ -9297,7 +9309,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="C322" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D322" s="34">
         <v>0.43243199999999998</v>
@@ -9310,7 +9322,7 @@
       <c r="A323" s="95"/>
       <c r="B323" s="93"/>
       <c r="C323" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D323" s="33">
         <v>0.296296</v>
@@ -9323,7 +9335,7 @@
       <c r="A324" s="95"/>
       <c r="B324" s="93"/>
       <c r="C324" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D324" s="33">
         <v>0.33333299999999999</v>
@@ -9336,7 +9348,7 @@
       <c r="A325" s="95"/>
       <c r="B325" s="94"/>
       <c r="C325" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D325" s="35">
         <v>0.1</v>
@@ -9351,7 +9363,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="C326" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D326" s="34">
         <v>0.264706</v>
@@ -9364,7 +9376,7 @@
       <c r="A327" s="95"/>
       <c r="B327" s="93"/>
       <c r="C327" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D327" s="33">
         <v>7.4074000000000001E-2</v>
@@ -9377,7 +9389,7 @@
       <c r="A328" s="95"/>
       <c r="B328" s="93"/>
       <c r="C328" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D328" s="33">
         <v>0.121212</v>
@@ -9390,7 +9402,7 @@
       <c r="A329" s="95"/>
       <c r="B329" s="94"/>
       <c r="C329" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D329" s="35">
         <v>4.1667000000000003E-2</v>
@@ -9405,7 +9417,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="C330" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D330" s="34">
         <v>4.4443999999999997E-2</v>
@@ -9418,20 +9430,20 @@
       <c r="A331" s="95"/>
       <c r="B331" s="93"/>
       <c r="C331" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D331" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E331" s="37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="332" spans="1:5">
       <c r="A332" s="95"/>
       <c r="B332" s="93"/>
       <c r="C332" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D332" s="33">
         <v>0.152174</v>
@@ -9444,7 +9456,7 @@
       <c r="A333" s="95"/>
       <c r="B333" s="94"/>
       <c r="C333" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D333" s="35">
         <v>0</v>
@@ -9459,33 +9471,33 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="C334" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D334" s="34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E334" s="36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="335" spans="1:5">
       <c r="A335" s="95"/>
       <c r="B335" s="93"/>
       <c r="C335" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D335" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E335" s="37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="336" spans="1:5">
       <c r="A336" s="95"/>
       <c r="B336" s="93"/>
       <c r="C336" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D336" s="33">
         <v>0.368421</v>
@@ -9498,7 +9510,7 @@
       <c r="A337" s="95"/>
       <c r="B337" s="94"/>
       <c r="C337" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D337" s="35">
         <v>0.13333300000000001</v>
@@ -9513,7 +9525,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="C338" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D338" s="34">
         <v>0.69696999999999998</v>
@@ -9526,7 +9538,7 @@
       <c r="A339" s="95"/>
       <c r="B339" s="93"/>
       <c r="C339" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D339" s="33">
         <v>0.59259300000000004</v>
@@ -9539,7 +9551,7 @@
       <c r="A340" s="95"/>
       <c r="B340" s="93"/>
       <c r="C340" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D340" s="33">
         <v>0.70454499999999998</v>
@@ -9552,7 +9564,7 @@
       <c r="A341" s="95"/>
       <c r="B341" s="94"/>
       <c r="C341" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D341" s="35">
         <v>0.63636400000000004</v>
@@ -9567,7 +9579,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="C342" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D342" s="34">
         <v>0.38461499999999998</v>
@@ -9580,7 +9592,7 @@
       <c r="A343" s="95"/>
       <c r="B343" s="93"/>
       <c r="C343" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D343" s="33">
         <v>0.14285700000000001</v>
@@ -9593,7 +9605,7 @@
       <c r="A344" s="95"/>
       <c r="B344" s="93"/>
       <c r="C344" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D344" s="33">
         <v>0</v>
@@ -9606,7 +9618,7 @@
       <c r="A345" s="95"/>
       <c r="B345" s="94"/>
       <c r="C345" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D345" s="35">
         <v>0.25</v>
@@ -9621,7 +9633,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="C346" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D346" s="34">
         <v>3.0303E-2</v>
@@ -9634,20 +9646,20 @@
       <c r="A347" s="95"/>
       <c r="B347" s="93"/>
       <c r="C347" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D347" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E347" s="37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="348" spans="1:5">
       <c r="A348" s="95"/>
       <c r="B348" s="93"/>
       <c r="C348" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D348" s="33">
         <v>0.171429</v>
@@ -9660,7 +9672,7 @@
       <c r="A349" s="95"/>
       <c r="B349" s="94"/>
       <c r="C349" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D349" s="35">
         <v>6.25E-2</v>
@@ -9675,7 +9687,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="C350" s="24" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="D350" s="34">
         <v>0.4</v>
@@ -9688,20 +9700,20 @@
       <c r="A351" s="95"/>
       <c r="B351" s="93"/>
       <c r="C351" s="8" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D351" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E351" s="37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="352" spans="1:5">
       <c r="A352" s="95"/>
       <c r="B352" s="93"/>
       <c r="C352" s="8" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="D352" s="33">
         <v>0.47368399999999999</v>
@@ -9714,7 +9726,7 @@
       <c r="A353" s="95"/>
       <c r="B353" s="94"/>
       <c r="C353" s="27" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D353" s="35">
         <v>0.461538</v>
@@ -9842,253 +9854,253 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="61" t="s">
-        <v>217</v>
-      </c>
-      <c r="B1" s="61" t="s">
+      <c r="A1" s="74" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="74" t="s">
+        <v>205</v>
+      </c>
+      <c r="F1" s="74" t="s">
+        <v>206</v>
+      </c>
+      <c r="G1" s="50"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="75">
+        <v>1</v>
+      </c>
+      <c r="B2" s="76" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="77">
+        <v>23.9138709677419</v>
+      </c>
+      <c r="D2" s="77">
+        <v>19.904301075268801</v>
+      </c>
+      <c r="E2" s="77">
+        <v>3.62088172043011</v>
+      </c>
+      <c r="F2" s="77">
+        <v>9.8097434965383901</v>
+      </c>
+      <c r="G2" s="51"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="75">
+        <v>3</v>
+      </c>
+      <c r="B3" s="76" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="77">
+        <v>71.996774193548404</v>
+      </c>
+      <c r="D3" s="77">
+        <v>12.489247311828001</v>
+      </c>
+      <c r="E3" s="77">
+        <v>2.0166881720430099</v>
+      </c>
+      <c r="F3" s="77">
+        <v>13.289870274379901</v>
+      </c>
+      <c r="G3" s="51"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="75">
+        <v>4</v>
+      </c>
+      <c r="B4" s="76" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="77">
+        <v>58.762903225806497</v>
+      </c>
+      <c r="D4" s="77">
+        <v>17.555913978494601</v>
+      </c>
+      <c r="E4" s="77">
+        <v>3.26145161290323</v>
+      </c>
+      <c r="F4" s="77">
+        <v>10.670492424171201</v>
+      </c>
+      <c r="G4" s="51"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="75">
+        <v>5</v>
+      </c>
+      <c r="B5" s="76" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="77">
+        <v>59.02</v>
+      </c>
+      <c r="D5" s="77">
+        <v>16.461290322580599</v>
+      </c>
+      <c r="E5" s="77">
+        <v>2.74702150537634</v>
+      </c>
+      <c r="F5" s="77">
+        <v>12.0388784868085</v>
+      </c>
+      <c r="G5" s="51"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="75">
+        <v>6</v>
+      </c>
+      <c r="B6" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="61" t="s">
-        <v>209</v>
-      </c>
-      <c r="F1" s="61" t="s">
-        <v>210</v>
-      </c>
-      <c r="G1" s="50"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="62">
-        <v>1</v>
-      </c>
-      <c r="B2" s="63" t="s">
+      <c r="C6" s="77">
+        <v>29.000967741935501</v>
+      </c>
+      <c r="D6" s="77">
+        <v>17.808602150537599</v>
+      </c>
+      <c r="E6" s="77">
+        <v>3.3919784946236602</v>
+      </c>
+      <c r="F6" s="77">
+        <v>10.863771875145201</v>
+      </c>
+      <c r="G6" s="51"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="75">
+        <v>7</v>
+      </c>
+      <c r="B7" s="76" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="77">
+        <v>29.7751612903226</v>
+      </c>
+      <c r="D7" s="77">
+        <v>13.1827956989247</v>
+      </c>
+      <c r="E7" s="77">
+        <v>2.4620430107526898</v>
+      </c>
+      <c r="F7" s="77">
+        <v>11.191736578258899</v>
+      </c>
+      <c r="G7" s="51"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="75">
+        <v>8</v>
+      </c>
+      <c r="B8" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="64">
-        <v>23.9138709677419</v>
-      </c>
-      <c r="D2" s="64">
-        <v>19.904301075268801</v>
-      </c>
-      <c r="E2" s="64">
-        <v>3.62088172043011</v>
-      </c>
-      <c r="F2" s="64">
-        <v>9.8097434965383901</v>
-      </c>
-      <c r="G2" s="51"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="62">
-        <v>3</v>
-      </c>
-      <c r="B3" s="63" t="s">
+      <c r="C8" s="77">
+        <v>35.9838709677419</v>
+      </c>
+      <c r="D8" s="77">
+        <v>16.6537634408602</v>
+      </c>
+      <c r="E8" s="77">
+        <v>3.10291397849462</v>
+      </c>
+      <c r="F8" s="77">
+        <v>9.2257199487345201</v>
+      </c>
+      <c r="G8" s="51"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="75">
+        <v>9</v>
+      </c>
+      <c r="B9" s="76" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="77">
+        <v>26.4954838709677</v>
+      </c>
+      <c r="D9" s="77">
+        <v>20.538709677419401</v>
+      </c>
+      <c r="E9" s="77">
+        <v>3.58602150537634</v>
+      </c>
+      <c r="F9" s="77">
+        <v>8.6708552293104102</v>
+      </c>
+      <c r="G9" s="51"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="75">
+        <v>10</v>
+      </c>
+      <c r="B10" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="64">
-        <v>71.996774193548404</v>
-      </c>
-      <c r="D3" s="64">
-        <v>12.489247311828001</v>
-      </c>
-      <c r="E3" s="64">
-        <v>2.0166881720430099</v>
-      </c>
-      <c r="F3" s="64">
-        <v>13.289870274379901</v>
-      </c>
-      <c r="G3" s="51"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="62">
-        <v>4</v>
-      </c>
-      <c r="B4" s="63" t="s">
+      <c r="C10" s="77">
+        <v>58.086451612903197</v>
+      </c>
+      <c r="D10" s="77">
+        <v>13.994623655913999</v>
+      </c>
+      <c r="E10" s="77">
+        <v>2.39647311827957</v>
+      </c>
+      <c r="F10" s="77">
+        <v>12.844082066747401</v>
+      </c>
+      <c r="G10" s="51"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="75">
+        <v>11</v>
+      </c>
+      <c r="B11" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="64">
-        <v>58.762903225806497</v>
-      </c>
-      <c r="D4" s="64">
-        <v>17.555913978494601</v>
-      </c>
-      <c r="E4" s="64">
-        <v>3.26145161290323</v>
-      </c>
-      <c r="F4" s="64">
-        <v>10.670492424171201</v>
-      </c>
-      <c r="G4" s="51"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="62">
-        <v>5</v>
-      </c>
-      <c r="B5" s="63" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="64">
-        <v>59.02</v>
-      </c>
-      <c r="D5" s="64">
-        <v>16.461290322580599</v>
-      </c>
-      <c r="E5" s="64">
-        <v>2.74702150537634</v>
-      </c>
-      <c r="F5" s="64">
-        <v>12.0388784868085</v>
-      </c>
-      <c r="G5" s="51"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="62">
-        <v>6</v>
-      </c>
-      <c r="B6" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="64">
-        <v>29.000967741935501</v>
-      </c>
-      <c r="D6" s="64">
-        <v>17.808602150537599</v>
-      </c>
-      <c r="E6" s="64">
-        <v>3.3919784946236602</v>
-      </c>
-      <c r="F6" s="64">
-        <v>10.863771875145201</v>
-      </c>
-      <c r="G6" s="51"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="62">
-        <v>7</v>
-      </c>
-      <c r="B7" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="64">
-        <v>29.7751612903226</v>
-      </c>
-      <c r="D7" s="64">
-        <v>13.1827956989247</v>
-      </c>
-      <c r="E7" s="64">
-        <v>2.4620430107526898</v>
-      </c>
-      <c r="F7" s="64">
-        <v>11.191736578258899</v>
-      </c>
-      <c r="G7" s="51"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="62">
-        <v>8</v>
-      </c>
-      <c r="B8" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="64">
-        <v>35.9838709677419</v>
-      </c>
-      <c r="D8" s="64">
-        <v>16.6537634408602</v>
-      </c>
-      <c r="E8" s="64">
-        <v>3.10291397849462</v>
-      </c>
-      <c r="F8" s="64">
-        <v>9.2257199487345201</v>
-      </c>
-      <c r="G8" s="51"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="62">
-        <v>9</v>
-      </c>
-      <c r="B9" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="64">
-        <v>26.4954838709677</v>
-      </c>
-      <c r="D9" s="64">
-        <v>20.538709677419401</v>
-      </c>
-      <c r="E9" s="64">
-        <v>3.58602150537634</v>
-      </c>
-      <c r="F9" s="64">
-        <v>8.6708552293104102</v>
-      </c>
-      <c r="G9" s="51"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="62">
-        <v>10</v>
-      </c>
-      <c r="B10" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="64">
-        <v>58.086451612903197</v>
-      </c>
-      <c r="D10" s="64">
-        <v>13.994623655913999</v>
-      </c>
-      <c r="E10" s="64">
-        <v>2.39647311827957</v>
-      </c>
-      <c r="F10" s="64">
-        <v>12.844082066747401</v>
-      </c>
-      <c r="G10" s="51"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="62">
-        <v>11</v>
-      </c>
-      <c r="B11" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" s="64">
+      <c r="C11" s="77">
         <v>53.365806451612897</v>
       </c>
-      <c r="D11" s="64">
+      <c r="D11" s="77">
         <v>15.9086021505376</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="77">
         <v>2.7985698924731199</v>
       </c>
-      <c r="F11" s="64">
+      <c r="F11" s="77">
         <v>11.139438061733999</v>
       </c>
       <c r="G11" s="51"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="62">
+      <c r="A12" s="75">
         <v>12</v>
       </c>
-      <c r="B12" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="64">
+      <c r="B12" s="76" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="77">
         <v>48.858709677419398</v>
       </c>
-      <c r="D12" s="64">
+      <c r="D12" s="77">
         <v>16.555913978494601</v>
       </c>
-      <c r="E12" s="64">
+      <c r="E12" s="77">
         <v>2.7627526881720401</v>
       </c>
-      <c r="F12" s="64">
+      <c r="F12" s="77">
         <v>11.0957376638142</v>
       </c>
       <c r="G12" s="51"/>
@@ -10112,21 +10124,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -10134,7 +10146,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>0.29174800000000001</v>
@@ -10148,7 +10160,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>0.15243599999999999</v>
@@ -10162,7 +10174,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>0.22004899999999999</v>
@@ -10176,7 +10188,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>0.21283299999999999</v>
@@ -10190,7 +10202,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>0.548655</v>
@@ -10204,7 +10216,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>0.200151</v>
@@ -10218,7 +10230,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>0.48843799999999998</v>
@@ -10232,7 +10244,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>0.32170900000000002</v>
@@ -10246,7 +10258,7 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11">
         <v>0.348632</v>
@@ -10260,7 +10272,7 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12">
         <v>0.27481</v>
@@ -10274,7 +10286,7 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13">
         <v>0.428871</v>
@@ -10288,7 +10300,7 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14">
         <v>0.26101999999999997</v>
@@ -10302,7 +10314,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15">
         <v>0.36661700000000003</v>
@@ -10316,7 +10328,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C16">
         <v>0.194489</v>
@@ -10330,7 +10342,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17">
         <v>0.36510300000000001</v>
@@ -10344,7 +10356,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18">
         <v>0.18803700000000001</v>
@@ -10358,7 +10370,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C19">
         <v>0.360765</v>
@@ -10372,7 +10384,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C20">
         <v>0.226073</v>
@@ -10386,7 +10398,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C21">
         <v>0.47406999999999999</v>
@@ -10400,7 +10412,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C22">
         <v>0.14495</v>
@@ -10414,7 +10426,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C23">
         <v>0.40722599999999998</v>
@@ -10428,7 +10440,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C24">
         <v>0.27180399999999999</v>
@@ -10442,7 +10454,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C25">
         <v>0.61926499999999995</v>
@@ -10456,7 +10468,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C26">
         <v>0.28196700000000002</v>
@@ -10470,7 +10482,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C27">
         <v>0.383241</v>
@@ -10484,7 +10496,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28">
         <v>0.18756800000000001</v>
@@ -10498,7 +10510,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29">
         <v>0.33255299999999999</v>
@@ -10512,7 +10524,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C30">
         <v>0.25049300000000002</v>
@@ -10526,7 +10538,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C31">
         <v>0.33940199999999998</v>
@@ -10540,7 +10552,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C32">
         <v>0.36240299999999998</v>
@@ -10554,7 +10566,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C33">
         <v>0.43322699999999997</v>
@@ -10568,13 +10580,13 @@
         <v>11.191736578258899</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C34">
         <v>0.10459</v>
       </c>
       <c r="D34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -10582,7 +10594,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C35">
         <v>0.313247</v>
@@ -10596,7 +10608,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C36">
         <v>0.28788399999999997</v>
@@ -10610,7 +10622,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C37">
         <v>0.46144800000000002</v>
@@ -10624,7 +10636,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C38">
         <v>0.24962699999999999</v>
@@ -10638,7 +10650,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C39">
         <v>0.30615399999999998</v>
@@ -10652,7 +10664,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C40">
         <v>0.28018500000000002</v>
@@ -10666,7 +10678,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C41">
         <v>0.45214900000000002</v>
@@ -10680,7 +10692,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C42">
         <v>0.25912499999999999</v>
@@ -10694,7 +10706,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C43">
         <v>0.42197699999999999</v>
@@ -10708,7 +10720,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C44">
         <v>0.26158199999999998</v>
@@ -10722,7 +10734,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C45">
         <v>0.42022500000000002</v>
@@ -10736,7 +10748,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C46">
         <v>0.26823599999999997</v>
@@ -10747,21 +10759,21 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B50" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C50" t="s">
         <v>26</v>
       </c>
       <c r="D50" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -10769,7 +10781,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C51">
         <v>6.3857999999999998E-2</v>
@@ -10783,7 +10795,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C52">
         <v>2.5021000000000002E-2</v>
@@ -10797,7 +10809,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C53">
         <v>4.2241000000000001E-2</v>
@@ -10811,7 +10823,7 @@
         <v>8.6708552293104102</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C54">
         <v>3.6832999999999998E-2</v>
@@ -10825,7 +10837,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C55">
         <v>0.160271</v>
@@ -10839,7 +10851,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C56">
         <v>6.0395999999999998E-2</v>
@@ -10853,7 +10865,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C57">
         <v>0.23596400000000001</v>
@@ -10867,7 +10879,7 @@
         <v>9.2257199487345201</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C58">
         <v>7.7830999999999997E-2</v>
@@ -10881,7 +10893,7 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C59">
         <v>0.19903699999999999</v>
@@ -10895,7 +10907,7 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="B60" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C60">
         <v>5.3915999999999999E-2</v>
@@ -10909,7 +10921,7 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C61">
         <v>0.22262199999999999</v>
@@ -10923,7 +10935,7 @@
         <v>9.8097434965383901</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C62">
         <v>5.9192000000000002E-2</v>
@@ -10937,7 +10949,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C63">
         <v>9.5061000000000007E-2</v>
@@ -10951,7 +10963,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="B64" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C64">
         <v>5.9311999999999997E-2</v>
@@ -10965,7 +10977,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C65">
         <v>8.8089000000000001E-2</v>
@@ -10979,7 +10991,7 @@
         <v>10.670492424171201</v>
       </c>
       <c r="B66" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C66">
         <v>4.9112000000000003E-2</v>
@@ -10993,7 +11005,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C67">
         <v>0.10459499999999999</v>
@@ -11007,7 +11019,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="B68" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C68">
         <v>3.9419999999999997E-2</v>
@@ -11021,7 +11033,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="B69" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C69">
         <v>0.46018999999999999</v>
@@ -11035,7 +11047,7 @@
         <v>10.863771875145201</v>
       </c>
       <c r="B70" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C70">
         <v>2.3754999999999998E-2</v>
@@ -11049,7 +11061,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C71">
         <v>0.155584</v>
@@ -11063,7 +11075,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="B72" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C72">
         <v>6.6855999999999999E-2</v>
@@ -11077,7 +11089,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C73">
         <v>0.17174700000000001</v>
@@ -11091,7 +11103,7 @@
         <v>11.0957376638142</v>
       </c>
       <c r="B74" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C74">
         <v>4.3452999999999999E-2</v>
@@ -11105,7 +11117,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="B75" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C75">
         <v>0.168125</v>
@@ -11119,7 +11131,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="B76" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C76">
         <v>4.1991000000000001E-2</v>
@@ -11133,7 +11145,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C77">
         <v>0.15321000000000001</v>
@@ -11147,7 +11159,7 @@
         <v>11.139438061733999</v>
       </c>
       <c r="B78" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C78">
         <v>4.4975000000000001E-2</v>
@@ -11161,7 +11173,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C79">
         <v>0.143877</v>
@@ -11175,7 +11187,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="B80" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C80">
         <v>8.5074999999999998E-2</v>
@@ -11189,7 +11201,7 @@
         <v>11.191736578258899</v>
       </c>
       <c r="B81" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C81">
         <v>0.111983</v>
@@ -11203,13 +11215,13 @@
         <v>11.191736578258899</v>
       </c>
       <c r="B82" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C82">
         <v>1.8679999999999999E-2</v>
       </c>
       <c r="D82" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -11217,7 +11229,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C83">
         <v>0.17408000000000001</v>
@@ -11231,7 +11243,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="B84" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C84">
         <v>8.7521000000000002E-2</v>
@@ -11245,7 +11257,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="B85" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C85">
         <v>0.180923</v>
@@ -11259,7 +11271,7 @@
         <v>12.0388784868085</v>
       </c>
       <c r="B86" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C86">
         <v>6.5479999999999997E-2</v>
@@ -11273,7 +11285,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="B87" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C87">
         <v>0.181534</v>
@@ -11287,7 +11299,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="B88" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C88">
         <v>5.1291999999999997E-2</v>
@@ -11301,7 +11313,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="B89" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C89">
         <v>0.177312</v>
@@ -11315,7 +11327,7 @@
         <v>12.844082066747401</v>
       </c>
       <c r="B90" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C90">
         <v>5.9066E-2</v>
@@ -11329,7 +11341,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="B91" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C91">
         <v>0.27409099999999997</v>
@@ -11343,7 +11355,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="B92" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C92">
         <v>9.8820000000000005E-2</v>
@@ -11357,7 +11369,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="B93" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C93">
         <v>0.21170700000000001</v>
@@ -11371,7 +11383,7 @@
         <v>13.289870274379901</v>
       </c>
       <c r="B94" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C94">
         <v>9.5465999999999995E-2</v>
